--- a/LLM_Extraction_and_CrossCritique/interactive-table/noteable_results/cat1_results/gt-vs-runs-with-filter-column-averages_pipeline1.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/noteable_results/cat1_results/gt-vs-runs-with-filter-column-averages_pipeline1.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\noteable_results\cat1_results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D96D08-28A4-4EC7-ADF0-D8C0F17FFB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="queries_with_averages" sheetId="1" r:id="rId1"/>
     <sheet name="per_row_per_run" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -5051,8 +5057,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5115,13 +5121,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5159,7 +5173,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -5193,6 +5207,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -5227,9 +5242,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5402,11 +5418,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="124.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5438,7 +5458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -5464,13 +5484,13 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J2">
-        <v>0.7407407407407408</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>0.74074074074074081</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -5499,10 +5519,10 @@
         <v>0.6</v>
       </c>
       <c r="J3">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5531,10 +5551,10 @@
         <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.5555555555555556</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -5554,19 +5574,19 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H5">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I5">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J5">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -5592,13 +5612,13 @@
         <v>0.5</v>
       </c>
       <c r="I6">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J6">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -5624,13 +5644,13 @@
         <v>0.5</v>
       </c>
       <c r="I7">
-        <v>0.6999999999999998</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="J7">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5656,13 +5676,13 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J8">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5694,7 +5714,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -5720,13 +5740,13 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="J10">
-        <v>0.6190476190476191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.61904761904761907</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -5755,10 +5775,10 @@
         <v>0.5</v>
       </c>
       <c r="J11">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -5784,13 +5804,13 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>0.6999999999999998</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="J12">
         <v>0.875</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -5816,13 +5836,13 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>0.6999999999999998</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="J13">
         <v>0.875</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -5848,13 +5868,13 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0.6999999999999998</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="J14">
         <v>0.875</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -5886,7 +5906,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -5918,7 +5938,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -5944,13 +5964,13 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J17">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -5976,13 +5996,13 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.6999999999999998</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="J18">
         <v>0.875</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -6008,13 +6028,13 @@
         <v>0.5</v>
       </c>
       <c r="I19">
-        <v>0.4666666666666666</v>
+        <v>0.46666666666666662</v>
       </c>
       <c r="J19">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -6046,7 +6066,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -6078,7 +6098,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -6110,7 +6130,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -6136,13 +6156,13 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J23">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -6174,7 +6194,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -6206,7 +6226,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -6226,19 +6246,19 @@
         <v>24</v>
       </c>
       <c r="G26">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J26">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -6270,7 +6290,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -6302,7 +6322,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -6334,7 +6354,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -6366,7 +6386,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -6398,7 +6418,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -6430,7 +6450,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -6462,7 +6482,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -6488,13 +6508,13 @@
         <v>0.5</v>
       </c>
       <c r="I34">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="J34">
-        <v>0.5416666666666666</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -6520,13 +6540,13 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>0.4666666666666666</v>
+        <v>0.46666666666666662</v>
       </c>
       <c r="J35">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -6558,7 +6578,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -6590,7 +6610,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -6616,13 +6636,13 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J38">
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -6654,7 +6674,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -6686,7 +6706,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -6715,10 +6735,10 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="J41">
-        <v>0.7916666666666666</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -6750,7 +6770,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -6782,7 +6802,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -6811,10 +6831,10 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="J44">
-        <v>0.7916666666666666</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -6840,13 +6860,13 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J45">
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -6872,13 +6892,13 @@
         <v>0.5</v>
       </c>
       <c r="I46">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J46">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -6904,13 +6924,13 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J47">
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -6936,13 +6956,13 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J48">
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -6968,13 +6988,13 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J49">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -7000,13 +7020,13 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J50">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -7032,13 +7052,13 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J51">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -7070,7 +7090,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -7096,13 +7116,13 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>0.4666666666666666</v>
+        <v>0.46666666666666662</v>
       </c>
       <c r="J53">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -7128,13 +7148,13 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J54">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -7166,7 +7186,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -7198,7 +7218,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -7230,7 +7250,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -7256,13 +7276,13 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>0.6111111111111112</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="J58">
         <v>0.625</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -7294,7 +7314,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -7314,10 +7334,10 @@
         <v>58</v>
       </c>
       <c r="G60">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H60">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I60">
         <v>0.5</v>
@@ -7326,7 +7346,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -7358,7 +7378,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -7384,13 +7404,13 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J62">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -7416,13 +7436,13 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J63">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -7454,7 +7474,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -7474,7 +7494,7 @@
         <v>63</v>
       </c>
       <c r="G65">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -7486,7 +7506,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -7506,19 +7526,19 @@
         <v>64</v>
       </c>
       <c r="G66">
-        <v>0.4444444444444444</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="H66">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I66">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J66">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -7550,7 +7570,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -7576,13 +7596,13 @@
         <v>0.5</v>
       </c>
       <c r="I68">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J68">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -7611,10 +7631,10 @@
         <v>0.5</v>
       </c>
       <c r="J69">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -7634,19 +7654,19 @@
         <v>68</v>
       </c>
       <c r="G70">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H70">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I70">
         <v>0.5</v>
       </c>
       <c r="J70">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -7678,7 +7698,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -7698,19 +7718,19 @@
         <v>70</v>
       </c>
       <c r="G72">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H72">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I72">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J72">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -7742,7 +7762,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -7768,13 +7788,13 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J74">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -7800,13 +7820,13 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J75">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -7838,7 +7858,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -7864,13 +7884,13 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J77">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -7902,7 +7922,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -7934,7 +7954,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -7960,13 +7980,13 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J80">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -7998,7 +8018,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -8030,7 +8050,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -8062,7 +8082,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -8094,7 +8114,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -8126,7 +8146,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -8146,19 +8166,19 @@
         <v>84</v>
       </c>
       <c r="G86">
-        <v>0.7777777777777777</v>
+        <v>0.77777777777777768</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J86">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -8184,13 +8204,13 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J87">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -8222,7 +8242,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -8242,7 +8262,7 @@
         <v>87</v>
       </c>
       <c r="G89">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -8254,7 +8274,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -8283,10 +8303,10 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="J90">
-        <v>0.7916666666666666</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -8312,13 +8332,13 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J91">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -8344,13 +8364,13 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J92">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -8382,7 +8402,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -8402,7 +8422,7 @@
         <v>92</v>
       </c>
       <c r="G94">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="H94">
         <v>0.5</v>
@@ -8414,7 +8434,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -8440,13 +8460,13 @@
         <v>0.5</v>
       </c>
       <c r="I95">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J95">
         <v>0.5</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -8472,13 +8492,13 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>0.5666666666666667</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="J96">
-        <v>0.7083333333333334</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -8504,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>0.4000000000000001</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="J97">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -8542,7 +8562,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -8574,7 +8594,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -8606,7 +8626,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -8635,7 +8655,7 @@
         <v>0.5</v>
       </c>
       <c r="J101">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -8644,11 +8664,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F301"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -8668,7 +8688,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8685,10 +8705,10 @@
         <v>0.7</v>
       </c>
       <c r="F2">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -8705,10 +8725,10 @@
         <v>0.7</v>
       </c>
       <c r="F3">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -8725,10 +8745,10 @@
         <v>0.6</v>
       </c>
       <c r="F4">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8745,10 +8765,10 @@
         <v>0.6</v>
       </c>
       <c r="F5">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8765,10 +8785,10 @@
         <v>0.6</v>
       </c>
       <c r="F6">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8785,10 +8805,10 @@
         <v>0.6</v>
       </c>
       <c r="F7">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8805,10 +8825,10 @@
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>0.5555555555555556</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8825,10 +8845,10 @@
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>0.5555555555555556</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8845,10 +8865,10 @@
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>0.5555555555555556</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -8856,19 +8876,19 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E11">
         <v>0.4</v>
       </c>
       <c r="F11">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -8876,19 +8896,19 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D12">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E12">
         <v>0.4</v>
       </c>
       <c r="F12">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>3</v>
       </c>
@@ -8896,19 +8916,19 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D13">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E13">
         <v>0.4</v>
       </c>
       <c r="F13">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>4</v>
       </c>
@@ -8928,7 +8948,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>4</v>
       </c>
@@ -8948,7 +8968,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>4</v>
       </c>
@@ -8968,7 +8988,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>5</v>
       </c>
@@ -8985,10 +9005,10 @@
         <v>0.7</v>
       </c>
       <c r="F17">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>5</v>
       </c>
@@ -9005,10 +9025,10 @@
         <v>0.7</v>
       </c>
       <c r="F18">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>5</v>
       </c>
@@ -9025,10 +9045,10 @@
         <v>0.7</v>
       </c>
       <c r="F19">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>6</v>
       </c>
@@ -9045,10 +9065,10 @@
         <v>0.4</v>
       </c>
       <c r="F20">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6</v>
       </c>
@@ -9065,10 +9085,10 @@
         <v>0.4</v>
       </c>
       <c r="F21">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>6</v>
       </c>
@@ -9085,10 +9105,10 @@
         <v>0.4</v>
       </c>
       <c r="F22">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>7</v>
       </c>
@@ -9108,7 +9128,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>7</v>
       </c>
@@ -9128,7 +9148,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -9148,7 +9168,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>8</v>
       </c>
@@ -9168,7 +9188,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>8</v>
       </c>
@@ -9188,7 +9208,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>8</v>
       </c>
@@ -9208,7 +9228,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>9</v>
       </c>
@@ -9225,10 +9245,10 @@
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>9</v>
       </c>
@@ -9245,10 +9265,10 @@
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>9</v>
       </c>
@@ -9265,10 +9285,10 @@
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>10</v>
       </c>
@@ -9288,7 +9308,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>10</v>
       </c>
@@ -9308,7 +9328,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>10</v>
       </c>
@@ -9328,7 +9348,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>11</v>
       </c>
@@ -9348,7 +9368,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>11</v>
       </c>
@@ -9368,7 +9388,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>11</v>
       </c>
@@ -9388,7 +9408,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>12</v>
       </c>
@@ -9408,7 +9428,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>12</v>
       </c>
@@ -9428,7 +9448,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>12</v>
       </c>
@@ -9448,7 +9468,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>13</v>
       </c>
@@ -9468,7 +9488,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>13</v>
       </c>
@@ -9488,7 +9508,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>13</v>
       </c>
@@ -9508,7 +9528,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14</v>
       </c>
@@ -9528,7 +9548,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14</v>
       </c>
@@ -9548,7 +9568,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14</v>
       </c>
@@ -9568,7 +9588,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>15</v>
       </c>
@@ -9585,10 +9605,10 @@
         <v>0.4</v>
       </c>
       <c r="F47">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>15</v>
       </c>
@@ -9605,10 +9625,10 @@
         <v>0.4</v>
       </c>
       <c r="F48">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>15</v>
       </c>
@@ -9625,10 +9645,10 @@
         <v>0.4</v>
       </c>
       <c r="F49">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>16</v>
       </c>
@@ -9648,7 +9668,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>16</v>
       </c>
@@ -9668,7 +9688,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>16</v>
       </c>
@@ -9688,7 +9708,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>17</v>
       </c>
@@ -9708,7 +9728,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>17</v>
       </c>
@@ -9728,7 +9748,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>17</v>
       </c>
@@ -9748,7 +9768,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>18</v>
       </c>
@@ -9768,7 +9788,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>18</v>
       </c>
@@ -9788,7 +9808,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>18</v>
       </c>
@@ -9808,7 +9828,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>19</v>
       </c>
@@ -9828,7 +9848,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>19</v>
       </c>
@@ -9848,7 +9868,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>19</v>
       </c>
@@ -9868,7 +9888,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>20</v>
       </c>
@@ -9888,7 +9908,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>20</v>
       </c>
@@ -9908,7 +9928,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>20</v>
       </c>
@@ -9928,7 +9948,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>21</v>
       </c>
@@ -9948,7 +9968,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>21</v>
       </c>
@@ -9968,7 +9988,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>21</v>
       </c>
@@ -9988,7 +10008,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>22</v>
       </c>
@@ -10008,7 +10028,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>22</v>
       </c>
@@ -10028,7 +10048,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>22</v>
       </c>
@@ -10048,7 +10068,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>23</v>
       </c>
@@ -10068,7 +10088,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>23</v>
       </c>
@@ -10088,7 +10108,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>23</v>
       </c>
@@ -10108,7 +10128,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>24</v>
       </c>
@@ -10116,7 +10136,7 @@
         <v>2</v>
       </c>
       <c r="C74">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -10128,7 +10148,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>24</v>
       </c>
@@ -10136,7 +10156,7 @@
         <v>3</v>
       </c>
       <c r="C75">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -10148,7 +10168,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>24</v>
       </c>
@@ -10156,7 +10176,7 @@
         <v>4</v>
       </c>
       <c r="C76">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -10168,7 +10188,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>25</v>
       </c>
@@ -10188,7 +10208,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>25</v>
       </c>
@@ -10208,7 +10228,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>25</v>
       </c>
@@ -10228,7 +10248,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>26</v>
       </c>
@@ -10248,7 +10268,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>26</v>
       </c>
@@ -10268,7 +10288,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>26</v>
       </c>
@@ -10288,7 +10308,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>27</v>
       </c>
@@ -10308,7 +10328,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>27</v>
       </c>
@@ -10328,7 +10348,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>27</v>
       </c>
@@ -10348,7 +10368,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>28</v>
       </c>
@@ -10368,7 +10388,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>28</v>
       </c>
@@ -10388,7 +10408,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>28</v>
       </c>
@@ -10408,7 +10428,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>29</v>
       </c>
@@ -10428,7 +10448,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>29</v>
       </c>
@@ -10448,7 +10468,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>29</v>
       </c>
@@ -10468,7 +10488,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>30</v>
       </c>
@@ -10488,7 +10508,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>30</v>
       </c>
@@ -10508,7 +10528,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>30</v>
       </c>
@@ -10528,7 +10548,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>31</v>
       </c>
@@ -10548,7 +10568,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>31</v>
       </c>
@@ -10568,7 +10588,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>31</v>
       </c>
@@ -10588,7 +10608,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>32</v>
       </c>
@@ -10608,7 +10628,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>32</v>
       </c>
@@ -10628,7 +10648,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>32</v>
       </c>
@@ -10648,7 +10668,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>33</v>
       </c>
@@ -10668,7 +10688,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>33</v>
       </c>
@@ -10688,7 +10708,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>33</v>
       </c>
@@ -10708,7 +10728,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>34</v>
       </c>
@@ -10728,7 +10748,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>34</v>
       </c>
@@ -10748,7 +10768,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>34</v>
       </c>
@@ -10768,7 +10788,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>35</v>
       </c>
@@ -10788,7 +10808,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>35</v>
       </c>
@@ -10808,7 +10828,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>35</v>
       </c>
@@ -10828,7 +10848,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>36</v>
       </c>
@@ -10848,7 +10868,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>36</v>
       </c>
@@ -10868,7 +10888,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>36</v>
       </c>
@@ -10888,7 +10908,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>37</v>
       </c>
@@ -10908,7 +10928,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>37</v>
       </c>
@@ -10928,7 +10948,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>37</v>
       </c>
@@ -10948,7 +10968,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>38</v>
       </c>
@@ -10968,7 +10988,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>38</v>
       </c>
@@ -10988,7 +11008,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>38</v>
       </c>
@@ -11008,7 +11028,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>39</v>
       </c>
@@ -11028,7 +11048,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>39</v>
       </c>
@@ -11048,7 +11068,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>39</v>
       </c>
@@ -11068,7 +11088,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>40</v>
       </c>
@@ -11088,7 +11108,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>40</v>
       </c>
@@ -11108,7 +11128,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>40</v>
       </c>
@@ -11128,7 +11148,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>41</v>
       </c>
@@ -11148,7 +11168,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>41</v>
       </c>
@@ -11168,7 +11188,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>41</v>
       </c>
@@ -11188,7 +11208,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>42</v>
       </c>
@@ -11208,7 +11228,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>42</v>
       </c>
@@ -11228,7 +11248,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>42</v>
       </c>
@@ -11248,7 +11268,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>43</v>
       </c>
@@ -11268,7 +11288,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>43</v>
       </c>
@@ -11288,7 +11308,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>43</v>
       </c>
@@ -11308,7 +11328,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>44</v>
       </c>
@@ -11328,7 +11348,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>44</v>
       </c>
@@ -11348,7 +11368,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>44</v>
       </c>
@@ -11368,7 +11388,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>45</v>
       </c>
@@ -11388,7 +11408,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>45</v>
       </c>
@@ -11408,7 +11428,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>45</v>
       </c>
@@ -11428,7 +11448,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>46</v>
       </c>
@@ -11448,7 +11468,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>46</v>
       </c>
@@ -11468,7 +11488,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>46</v>
       </c>
@@ -11488,7 +11508,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>47</v>
       </c>
@@ -11508,7 +11528,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>47</v>
       </c>
@@ -11528,7 +11548,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>47</v>
       </c>
@@ -11548,7 +11568,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>48</v>
       </c>
@@ -11568,7 +11588,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>48</v>
       </c>
@@ -11588,7 +11608,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>48</v>
       </c>
@@ -11608,7 +11628,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>49</v>
       </c>
@@ -11628,7 +11648,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>49</v>
       </c>
@@ -11648,7 +11668,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>49</v>
       </c>
@@ -11668,7 +11688,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>50</v>
       </c>
@@ -11688,7 +11708,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>50</v>
       </c>
@@ -11708,7 +11728,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>50</v>
       </c>
@@ -11728,7 +11748,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>51</v>
       </c>
@@ -11748,7 +11768,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>51</v>
       </c>
@@ -11768,7 +11788,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>51</v>
       </c>
@@ -11788,7 +11808,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>52</v>
       </c>
@@ -11808,7 +11828,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>52</v>
       </c>
@@ -11828,7 +11848,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>52</v>
       </c>
@@ -11848,7 +11868,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>53</v>
       </c>
@@ -11868,7 +11888,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>53</v>
       </c>
@@ -11888,7 +11908,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>53</v>
       </c>
@@ -11908,7 +11928,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>54</v>
       </c>
@@ -11928,7 +11948,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>54</v>
       </c>
@@ -11948,7 +11968,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>54</v>
       </c>
@@ -11968,7 +11988,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>55</v>
       </c>
@@ -11988,7 +12008,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>55</v>
       </c>
@@ -12008,7 +12028,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>55</v>
       </c>
@@ -12028,7 +12048,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>56</v>
       </c>
@@ -12048,7 +12068,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>56</v>
       </c>
@@ -12068,7 +12088,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>56</v>
       </c>
@@ -12082,13 +12102,13 @@
         <v>1</v>
       </c>
       <c r="E172">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F172">
         <v>0.625</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>57</v>
       </c>
@@ -12108,7 +12128,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>57</v>
       </c>
@@ -12128,7 +12148,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>57</v>
       </c>
@@ -12148,7 +12168,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>58</v>
       </c>
@@ -12168,7 +12188,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>58</v>
       </c>
@@ -12188,7 +12208,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>58</v>
       </c>
@@ -12208,7 +12228,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>59</v>
       </c>
@@ -12228,7 +12248,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>59</v>
       </c>
@@ -12248,7 +12268,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>59</v>
       </c>
@@ -12268,7 +12288,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>60</v>
       </c>
@@ -12285,10 +12305,10 @@
         <v>0.4</v>
       </c>
       <c r="F182">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>60</v>
       </c>
@@ -12305,10 +12325,10 @@
         <v>0.4</v>
       </c>
       <c r="F183">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>60</v>
       </c>
@@ -12325,10 +12345,10 @@
         <v>0.4</v>
       </c>
       <c r="F184">
-        <v>0.4444444444444444</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>61</v>
       </c>
@@ -12348,7 +12368,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>61</v>
       </c>
@@ -12368,7 +12388,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>61</v>
       </c>
@@ -12388,7 +12408,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>62</v>
       </c>
@@ -12408,7 +12428,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>62</v>
       </c>
@@ -12428,7 +12448,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>62</v>
       </c>
@@ -12448,7 +12468,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>63</v>
       </c>
@@ -12468,7 +12488,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>63</v>
       </c>
@@ -12488,7 +12508,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>63</v>
       </c>
@@ -12508,7 +12528,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>64</v>
       </c>
@@ -12516,7 +12536,7 @@
         <v>2</v>
       </c>
       <c r="C194">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -12528,7 +12548,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>64</v>
       </c>
@@ -12536,7 +12556,7 @@
         <v>3</v>
       </c>
       <c r="C195">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D195">
         <v>0.5</v>
@@ -12548,7 +12568,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>64</v>
       </c>
@@ -12556,7 +12576,7 @@
         <v>4</v>
       </c>
       <c r="C196">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D196">
         <v>0.5</v>
@@ -12568,7 +12588,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>65</v>
       </c>
@@ -12588,7 +12608,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>65</v>
       </c>
@@ -12608,7 +12628,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>65</v>
       </c>
@@ -12628,7 +12648,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>66</v>
       </c>
@@ -12648,7 +12668,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>66</v>
       </c>
@@ -12668,7 +12688,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>66</v>
       </c>
@@ -12688,7 +12708,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>67</v>
       </c>
@@ -12705,10 +12725,10 @@
         <v>0.5</v>
       </c>
       <c r="F203">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>67</v>
       </c>
@@ -12725,10 +12745,10 @@
         <v>0.5</v>
       </c>
       <c r="F204">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>67</v>
       </c>
@@ -12745,10 +12765,10 @@
         <v>0.5</v>
       </c>
       <c r="F205">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>68</v>
       </c>
@@ -12759,16 +12779,16 @@
         <v>0.5</v>
       </c>
       <c r="D206">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E206">
         <v>0.5</v>
       </c>
       <c r="F206">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>68</v>
       </c>
@@ -12779,16 +12799,16 @@
         <v>1</v>
       </c>
       <c r="D207">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E207">
         <v>0.5</v>
       </c>
       <c r="F207">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>68</v>
       </c>
@@ -12799,16 +12819,16 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E208">
         <v>0.5</v>
       </c>
       <c r="F208">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>69</v>
       </c>
@@ -12828,7 +12848,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>69</v>
       </c>
@@ -12848,7 +12868,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>69</v>
       </c>
@@ -12868,7 +12888,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>70</v>
       </c>
@@ -12885,10 +12905,10 @@
         <v>0.5</v>
       </c>
       <c r="F212">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>70</v>
       </c>
@@ -12905,10 +12925,10 @@
         <v>1</v>
       </c>
       <c r="F213">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>70</v>
       </c>
@@ -12925,10 +12945,10 @@
         <v>0.5</v>
       </c>
       <c r="F214">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>71</v>
       </c>
@@ -12948,7 +12968,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>71</v>
       </c>
@@ -12968,7 +12988,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>71</v>
       </c>
@@ -12988,7 +13008,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>72</v>
       </c>
@@ -13008,7 +13028,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>72</v>
       </c>
@@ -13028,7 +13048,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>72</v>
       </c>
@@ -13048,7 +13068,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>73</v>
       </c>
@@ -13068,7 +13088,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>73</v>
       </c>
@@ -13088,7 +13108,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>73</v>
       </c>
@@ -13108,7 +13128,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>74</v>
       </c>
@@ -13128,7 +13148,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>74</v>
       </c>
@@ -13148,7 +13168,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>74</v>
       </c>
@@ -13168,7 +13188,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>75</v>
       </c>
@@ -13188,7 +13208,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>75</v>
       </c>
@@ -13208,7 +13228,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>75</v>
       </c>
@@ -13228,7 +13248,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>76</v>
       </c>
@@ -13248,7 +13268,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>76</v>
       </c>
@@ -13268,7 +13288,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>76</v>
       </c>
@@ -13288,7 +13308,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>77</v>
       </c>
@@ -13308,7 +13328,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>77</v>
       </c>
@@ -13328,7 +13348,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>77</v>
       </c>
@@ -13348,7 +13368,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>78</v>
       </c>
@@ -13368,7 +13388,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>78</v>
       </c>
@@ -13388,7 +13408,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>78</v>
       </c>
@@ -13408,7 +13428,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>79</v>
       </c>
@@ -13428,7 +13448,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>79</v>
       </c>
@@ -13448,7 +13468,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>79</v>
       </c>
@@ -13468,7 +13488,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>80</v>
       </c>
@@ -13488,7 +13508,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>80</v>
       </c>
@@ -13508,7 +13528,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>80</v>
       </c>
@@ -13528,7 +13548,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>81</v>
       </c>
@@ -13548,7 +13568,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>81</v>
       </c>
@@ -13568,7 +13588,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>81</v>
       </c>
@@ -13588,7 +13608,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>82</v>
       </c>
@@ -13608,7 +13628,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>82</v>
       </c>
@@ -13628,7 +13648,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>82</v>
       </c>
@@ -13648,7 +13668,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>83</v>
       </c>
@@ -13668,7 +13688,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>83</v>
       </c>
@@ -13688,7 +13708,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>83</v>
       </c>
@@ -13708,7 +13728,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>84</v>
       </c>
@@ -13716,7 +13736,7 @@
         <v>2</v>
       </c>
       <c r="C254">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -13728,7 +13748,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>84</v>
       </c>
@@ -13736,7 +13756,7 @@
         <v>3</v>
       </c>
       <c r="C255">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -13748,7 +13768,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>84</v>
       </c>
@@ -13768,7 +13788,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>85</v>
       </c>
@@ -13788,7 +13808,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>85</v>
       </c>
@@ -13808,7 +13828,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>85</v>
       </c>
@@ -13828,7 +13848,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>86</v>
       </c>
@@ -13848,7 +13868,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>86</v>
       </c>
@@ -13868,7 +13888,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>86</v>
       </c>
@@ -13888,7 +13908,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>87</v>
       </c>
@@ -13896,7 +13916,7 @@
         <v>2</v>
       </c>
       <c r="C263">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -13908,7 +13928,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>87</v>
       </c>
@@ -13916,7 +13936,7 @@
         <v>3</v>
       </c>
       <c r="C264">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -13928,7 +13948,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>87</v>
       </c>
@@ -13936,7 +13956,7 @@
         <v>4</v>
       </c>
       <c r="C265">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -13948,7 +13968,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>88</v>
       </c>
@@ -13968,7 +13988,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>88</v>
       </c>
@@ -13988,7 +14008,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>88</v>
       </c>
@@ -14008,7 +14028,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>89</v>
       </c>
@@ -14028,7 +14048,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>89</v>
       </c>
@@ -14048,7 +14068,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>89</v>
       </c>
@@ -14068,7 +14088,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>90</v>
       </c>
@@ -14088,7 +14108,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>90</v>
       </c>
@@ -14108,7 +14128,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>90</v>
       </c>
@@ -14128,7 +14148,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>91</v>
       </c>
@@ -14148,7 +14168,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>91</v>
       </c>
@@ -14168,7 +14188,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>91</v>
       </c>
@@ -14188,7 +14208,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>92</v>
       </c>
@@ -14196,7 +14216,7 @@
         <v>2</v>
       </c>
       <c r="C278">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D278">
         <v>0.5</v>
@@ -14208,7 +14228,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>92</v>
       </c>
@@ -14216,7 +14236,7 @@
         <v>3</v>
       </c>
       <c r="C279">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D279">
         <v>0.5</v>
@@ -14228,7 +14248,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>92</v>
       </c>
@@ -14236,7 +14256,7 @@
         <v>4</v>
       </c>
       <c r="C280">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D280">
         <v>0.5</v>
@@ -14248,7 +14268,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>93</v>
       </c>
@@ -14268,7 +14288,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>93</v>
       </c>
@@ -14288,7 +14308,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>93</v>
       </c>
@@ -14308,7 +14328,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>94</v>
       </c>
@@ -14328,7 +14348,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>94</v>
       </c>
@@ -14348,7 +14368,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>94</v>
       </c>
@@ -14368,7 +14388,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>95</v>
       </c>
@@ -14388,7 +14408,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>95</v>
       </c>
@@ -14408,7 +14428,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>95</v>
       </c>
@@ -14428,7 +14448,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>96</v>
       </c>
@@ -14448,7 +14468,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>96</v>
       </c>
@@ -14468,7 +14488,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>96</v>
       </c>
@@ -14488,7 +14508,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>97</v>
       </c>
@@ -14508,7 +14528,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>97</v>
       </c>
@@ -14528,7 +14548,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>97</v>
       </c>
@@ -14548,7 +14568,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>98</v>
       </c>
@@ -14568,7 +14588,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>98</v>
       </c>
@@ -14588,7 +14608,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>98</v>
       </c>
@@ -14608,7 +14628,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>99</v>
       </c>
@@ -14625,10 +14645,10 @@
         <v>0.5</v>
       </c>
       <c r="F299">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>99</v>
       </c>
@@ -14645,10 +14665,10 @@
         <v>0.5</v>
       </c>
       <c r="F300">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>99</v>
       </c>
@@ -14665,7 +14685,7 @@
         <v>0.5</v>
       </c>
       <c r="F301">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
